--- a/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.10/Food use (.1000)/Argentina.xlsx
+++ b/data/raw/관세청/Import Export Performance by Commodity and Country(GW)/Soybean Oil/1507.10/Food use (.1000)/Argentina.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\9개년_품목별 국가별 수출입실적\대두유\1507.10\식품용(.1000)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\데이터플랫폼팀\00 데이터플랫폼팀_공유\데이터플랫폼팀(23.03~)\08 데이터 분석\00 분석과제정의서\☆구매\수입원료\대두유\데이터\외부\경제, 무역\관세청\15개년_품목별 국가별 수출입실적\대두유\1507.10\식품용(.1000)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="11640" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25125" windowHeight="11640" firstSheet="3" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="2010년" sheetId="11" r:id="rId1"/>
@@ -939,18 +939,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>0</v>
-      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2457,18 +2449,10 @@
         <f t="shared" ref="B3:B14" si="0">C3-E3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="2">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
@@ -2832,18 +2816,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6" s="2">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0</v>
-      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -2853,18 +2829,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -2979,18 +2947,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -3165,12 +3125,20 @@
       </c>
       <c r="B9" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+        <v>-2820142</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2820142</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2499890</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -3243,7 +3211,7 @@
       </c>
       <c r="B15" s="5">
         <f>SUM(B3:B14)</f>
-        <v>-8575999</v>
+        <v>-11396141</v>
       </c>
       <c r="C15" s="5">
         <f t="shared" ref="C15:F15" si="1">SUM(C3:C14)</f>
@@ -3255,11 +3223,11 @@
       </c>
       <c r="E15" s="5">
         <f t="shared" si="1"/>
-        <v>8575999</v>
+        <v>11396141</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="1"/>
-        <v>7499934</v>
+        <v>9999824</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -5430,23 +5398,23 @@
         <v>13</v>
       </c>
       <c r="B15" s="5">
-        <f t="shared" ref="B15" si="1">E15-C15</f>
+        <f>SUM(B3:B14)</f>
+        <v>-79138060</v>
+      </c>
+      <c r="C15" s="5">
+        <f t="shared" ref="C15:F15" si="1">SUM(C3:C14)</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <f t="shared" si="1"/>
         <v>79138060</v>
       </c>
-      <c r="C15" s="5">
-        <f t="shared" ref="C15" si="2">SUM(C3:C14)</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="5">
-        <f t="shared" ref="D15" si="3">SUM(D3:D14)</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="5">
-        <f t="shared" ref="E15:F15" si="4">SUM(E3:E14)</f>
-        <v>79138060</v>
-      </c>
       <c r="F15" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="1"/>
         <v>94162253</v>
       </c>
     </row>
